--- a/tools/language/多语言对照表.xlsx
+++ b/tools/language/多语言对照表.xlsx
@@ -395,7 +395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB554"/>
+  <dimension ref="A1:AB556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31.6299991607666" customWidth="1" min="1" max="1"/>
@@ -1010,27 +1010,27 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>还没有填写宝宝生日，记得补上哦</t>
+          <t>添加生日，查看宝宝月龄</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>You haven’t filled in your baby’s birthday yet, please remember to fill it in.</t>
+          <t>Add a birthday to see your baby’s age</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>還沒填寶寶生日，記得補上哦</t>
+          <t>新增生日，查看寶寶月齡</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>赤ちゃんの誕生日をまだ記入していない場合は、忘れずに記入してください。</t>
+          <t>誕生日を追加して月齢を表示</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>아직 아기의 생일을 입력하지 않으셨으니 꼭 입력해주세요.</t>
+          <t>생일을 추가하고 월령 확인하기</t>
         </is>
       </c>
       <c r="G10" s="5" t="n"/>
@@ -29109,6 +29109,70 @@
       <c r="F554" s="5" t="inlineStr">
         <is>
           <t>%1$s, 기록 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="5" t="inlineStr">
+        <is>
+          <t>record_draft_already_saved</t>
+        </is>
+      </c>
+      <c r="B555" s="5" t="inlineStr">
+        <is>
+          <t>已保存过此草稿，请从时间轴编辑原记录</t>
+        </is>
+      </c>
+      <c r="C555" s="5" t="inlineStr">
+        <is>
+          <t>Already saved. Edit the original entry in the timeline.</t>
+        </is>
+      </c>
+      <c r="D555" s="5" t="inlineStr">
+        <is>
+          <t>已儲存過此草稿，請從時間軸編輯原記錄</t>
+        </is>
+      </c>
+      <c r="E555" s="5" t="inlineStr">
+        <is>
+          <t>保存済みです。タイムラインから元の記録を編集してください</t>
+        </is>
+      </c>
+      <c r="F555" s="5" t="inlineStr">
+        <is>
+          <t>이미 저장된 기록이에요. 타임라인에서 원래 기록을 수정해 주세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="5" t="inlineStr">
+        <is>
+          <t>record_draft_record_deleted</t>
+        </is>
+      </c>
+      <c r="B556" s="5" t="inlineStr">
+        <is>
+          <t>原记录已删除，请重新打开记录页创建记录</t>
+        </is>
+      </c>
+      <c r="C556" s="5" t="inlineStr">
+        <is>
+          <t>Original entry deleted. Reopen this form to add a new entry.</t>
+        </is>
+      </c>
+      <c r="D556" s="5" t="inlineStr">
+        <is>
+          <t>原記錄已刪除，請重新開啟記錄頁建立記錄</t>
+        </is>
+      </c>
+      <c r="E556" s="5" t="inlineStr">
+        <is>
+          <t>元の記録は削除されています。記録画面を開き直して新しく作成してください</t>
+        </is>
+      </c>
+      <c r="F556" s="5" t="inlineStr">
+        <is>
+          <t>원래 기록이 삭제되었어요. 기록 화면을 다시 열어 새 기록을 만들어 주세요</t>
         </is>
       </c>
     </row>

--- a/tools/language/多语言对照表.xlsx
+++ b/tools/language/多语言对照表.xlsx
@@ -395,7 +395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB556"/>
+  <dimension ref="A1:AB560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31.6299991607666" customWidth="1" min="1" max="1"/>
@@ -29173,6 +29173,134 @@
       <c r="F556" s="5" t="inlineStr">
         <is>
           <t>원래 기록이 삭제되었어요. 기록 화면을 다시 열어 새 기록을 만들어 주세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="5" t="inlineStr">
+        <is>
+          <t>baby_profile_save_conflict</t>
+        </is>
+      </c>
+      <c r="B557" s="5" t="inlineStr">
+        <is>
+          <t>这份资料已保存，请重新打开宝宝资料进行修改</t>
+        </is>
+      </c>
+      <c r="C557" s="5" t="inlineStr">
+        <is>
+          <t>This profile is already saved. Reopen your baby’s profile to edit it.</t>
+        </is>
+      </c>
+      <c r="D557" s="5" t="inlineStr">
+        <is>
+          <t>這份資料已儲存，請重新開啟寶寶資料進行修改</t>
+        </is>
+      </c>
+      <c r="E557" s="5" t="inlineStr">
+        <is>
+          <t>このプロフィールは保存済みです。編集するには赤ちゃんのプロフィールを開き直してください</t>
+        </is>
+      </c>
+      <c r="F557" s="5" t="inlineStr">
+        <is>
+          <t>이미 저장된 프로필이에요. 수정하려면 아기 프로필을 다시 열어 주세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="5" t="inlineStr">
+        <is>
+          <t>baby_profile_deleted</t>
+        </is>
+      </c>
+      <c r="B558" s="5" t="inlineStr">
+        <is>
+          <t>该宝宝已删除，请返回后重新创建</t>
+        </is>
+      </c>
+      <c r="C558" s="5" t="inlineStr">
+        <is>
+          <t>This baby’s profile was deleted. Go back to create a new one.</t>
+        </is>
+      </c>
+      <c r="D558" s="5" t="inlineStr">
+        <is>
+          <t>該寶寶已刪除，請返回後重新建立</t>
+        </is>
+      </c>
+      <c r="E558" s="5" t="inlineStr">
+        <is>
+          <t>この赤ちゃんのプロフィールは削除されています。戻って新しく作成してください</t>
+        </is>
+      </c>
+      <c r="F558" s="5" t="inlineStr">
+        <is>
+          <t>이 아기의 프로필이 삭제되었어요. 돌아가서 새로 만들어 주세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="5" t="inlineStr">
+        <is>
+          <t>baby_age_birthdate_missing</t>
+        </is>
+      </c>
+      <c r="B559" s="5" t="inlineStr">
+        <is>
+          <t>生日未设置</t>
+        </is>
+      </c>
+      <c r="C559" s="5" t="inlineStr">
+        <is>
+          <t>Birthday not set</t>
+        </is>
+      </c>
+      <c r="D559" s="5" t="inlineStr">
+        <is>
+          <t>生日未設定</t>
+        </is>
+      </c>
+      <c r="E559" s="5" t="inlineStr">
+        <is>
+          <t>誕生日未設定</t>
+        </is>
+      </c>
+      <c r="F559" s="5" t="inlineStr">
+        <is>
+          <t>생일 미설정</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="5" t="inlineStr">
+        <is>
+          <t>baby_age_not_born_yet</t>
+        </is>
+      </c>
+      <c r="B560" s="5" t="inlineStr">
+        <is>
+          <t>尚未出生</t>
+        </is>
+      </c>
+      <c r="C560" s="5" t="inlineStr">
+        <is>
+          <t>Not born yet</t>
+        </is>
+      </c>
+      <c r="D560" s="5" t="inlineStr">
+        <is>
+          <t>尚未出生</t>
+        </is>
+      </c>
+      <c r="E560" s="5" t="inlineStr">
+        <is>
+          <t>出生前</t>
+        </is>
+      </c>
+      <c r="F560" s="5" t="inlineStr">
+        <is>
+          <t>아직 태어나지 않았어요</t>
         </is>
       </c>
     </row>

--- a/tools/language/多语言对照表.xlsx
+++ b/tools/language/多语言对照表.xlsx
@@ -15919,7 +15919,7 @@
       </c>
       <c r="C286" s="5" t="inlineStr">
         <is>
-          <t>since last time</t>
+          <t>Since last</t>
         </is>
       </c>
       <c r="D286" s="5" t="inlineStr">
@@ -16081,7 +16081,7 @@
       </c>
       <c r="C289" s="5" t="inlineStr">
         <is>
-          <t>next prediction</t>
+          <t>Next prediction</t>
         </is>
       </c>
       <c r="D289" s="5" t="inlineStr">
@@ -16184,27 +16184,27 @@
       </c>
       <c r="B291" s="5" t="inlineStr">
         <is>
-          <t>下次喂奶 %1$s~%2$s</t>
+          <t>喂奶 %1$s–%2$s</t>
         </is>
       </c>
       <c r="C291" s="5" t="inlineStr">
         <is>
-          <t>Next feeding %1$s~%2$s</t>
+          <t>Feeding %1$s–%2$s</t>
         </is>
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>下次餵奶 %1$s~%2$s</t>
+          <t>餵奶 %1$s–%2$s</t>
         </is>
       </c>
       <c r="E291" s="5" t="inlineStr">
         <is>
-          <t>次の給餌 %1$s~%2$s</t>
+          <t>授乳 %1$s–%2$s</t>
         </is>
       </c>
       <c r="F291" s="5" t="inlineStr">
         <is>
-          <t>다음 수유 %1$s~%2$s</t>
+          <t>수유 %1$s–%2$s</t>
         </is>
       </c>
       <c r="G291" s="5" t="n"/>
@@ -16292,27 +16292,27 @@
       </c>
       <c r="B293" s="5" t="inlineStr">
         <is>
-          <t>下次睡觉 %1$s~%2$s</t>
+          <t>睡觉 %1$s–%2$s</t>
         </is>
       </c>
       <c r="C293" s="5" t="inlineStr">
         <is>
-          <t>Next sleep %1$s~%2$s</t>
+          <t>Sleep %1$s–%2$s</t>
         </is>
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>下次睡覺 %1$s~%2$s</t>
+          <t>睡覺 %1$s–%2$s</t>
         </is>
       </c>
       <c r="E293" s="5" t="inlineStr">
         <is>
-          <t>次の睡眠 %1$s~%2$s</t>
+          <t>睡眠 %1$s–%2$s</t>
         </is>
       </c>
       <c r="F293" s="5" t="inlineStr">
         <is>
-          <t>다음 수면 %1$s~%2$s</t>
+          <t>수면 %1$s–%2$s</t>
         </is>
       </c>
       <c r="G293" s="5" t="n"/>
@@ -16351,7 +16351,7 @@
       </c>
       <c r="C294" s="5" t="inlineStr">
         <is>
-          <t>At most %1$s left</t>
+          <t>Within %1$s</t>
         </is>
       </c>
       <c r="D294" s="5" t="inlineStr">

--- a/tools/language/多语言对照表.xlsx
+++ b/tools/language/多语言对照表.xlsx
@@ -395,7 +395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB560"/>
+  <dimension ref="A1:AB566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31.6299991607666" customWidth="1" min="1" max="1"/>
@@ -29301,6 +29301,198 @@
       <c r="F560" s="5" t="inlineStr">
         <is>
           <t>아직 태어나지 않았어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="5" t="inlineStr">
+        <is>
+          <t>picker_year_accessibility_format</t>
+        </is>
+      </c>
+      <c r="B561" s="5" t="inlineStr">
+        <is>
+          <t>%1$d年</t>
+        </is>
+      </c>
+      <c r="C561" s="5" t="inlineStr">
+        <is>
+          <t>Year %1$d</t>
+        </is>
+      </c>
+      <c r="D561" s="5" t="inlineStr">
+        <is>
+          <t>%1$d年</t>
+        </is>
+      </c>
+      <c r="E561" s="5" t="inlineStr">
+        <is>
+          <t>%1$d年</t>
+        </is>
+      </c>
+      <c r="F561" s="5" t="inlineStr">
+        <is>
+          <t>%1$d년</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="5" t="inlineStr">
+        <is>
+          <t>picker_month_accessibility_format</t>
+        </is>
+      </c>
+      <c r="B562" s="5" t="inlineStr">
+        <is>
+          <t>%1$d月</t>
+        </is>
+      </c>
+      <c r="C562" s="5" t="inlineStr">
+        <is>
+          <t>Month %1$d</t>
+        </is>
+      </c>
+      <c r="D562" s="5" t="inlineStr">
+        <is>
+          <t>%1$d月</t>
+        </is>
+      </c>
+      <c r="E562" s="5" t="inlineStr">
+        <is>
+          <t>%1$d月</t>
+        </is>
+      </c>
+      <c r="F562" s="5" t="inlineStr">
+        <is>
+          <t>%1$d월</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="5" t="inlineStr">
+        <is>
+          <t>picker_day_accessibility_format</t>
+        </is>
+      </c>
+      <c r="B563" s="5" t="inlineStr">
+        <is>
+          <t>%1$d日</t>
+        </is>
+      </c>
+      <c r="C563" s="5" t="inlineStr">
+        <is>
+          <t>Day %1$d</t>
+        </is>
+      </c>
+      <c r="D563" s="5" t="inlineStr">
+        <is>
+          <t>%1$d日</t>
+        </is>
+      </c>
+      <c r="E563" s="5" t="inlineStr">
+        <is>
+          <t>%1$d日</t>
+        </is>
+      </c>
+      <c r="F563" s="5" t="inlineStr">
+        <is>
+          <t>%1$d일</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="5" t="inlineStr">
+        <is>
+          <t>picker_hour_accessibility_format</t>
+        </is>
+      </c>
+      <c r="B564" s="5" t="inlineStr">
+        <is>
+          <t>%1$d时</t>
+        </is>
+      </c>
+      <c r="C564" s="5" t="inlineStr">
+        <is>
+          <t>Hour %1$d</t>
+        </is>
+      </c>
+      <c r="D564" s="5" t="inlineStr">
+        <is>
+          <t>%1$d時</t>
+        </is>
+      </c>
+      <c r="E564" s="5" t="inlineStr">
+        <is>
+          <t>%1$d時</t>
+        </is>
+      </c>
+      <c r="F564" s="5" t="inlineStr">
+        <is>
+          <t>%1$d시</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="5" t="inlineStr">
+        <is>
+          <t>picker_minute_accessibility_format</t>
+        </is>
+      </c>
+      <c r="B565" s="5" t="inlineStr">
+        <is>
+          <t>%1$d分</t>
+        </is>
+      </c>
+      <c r="C565" s="5" t="inlineStr">
+        <is>
+          <t>Minute %1$d</t>
+        </is>
+      </c>
+      <c r="D565" s="5" t="inlineStr">
+        <is>
+          <t>%1$d分</t>
+        </is>
+      </c>
+      <c r="E565" s="5" t="inlineStr">
+        <is>
+          <t>%1$d分</t>
+        </is>
+      </c>
+      <c r="F565" s="5" t="inlineStr">
+        <is>
+          <t>%1$d분</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="5" t="inlineStr">
+        <is>
+          <t>picker_second_accessibility_format</t>
+        </is>
+      </c>
+      <c r="B566" s="5" t="inlineStr">
+        <is>
+          <t>%1$d秒</t>
+        </is>
+      </c>
+      <c r="C566" s="5" t="inlineStr">
+        <is>
+          <t>Second %1$d</t>
+        </is>
+      </c>
+      <c r="D566" s="5" t="inlineStr">
+        <is>
+          <t>%1$d秒</t>
+        </is>
+      </c>
+      <c r="E566" s="5" t="inlineStr">
+        <is>
+          <t>%1$d秒</t>
+        </is>
+      </c>
+      <c r="F566" s="5" t="inlineStr">
+        <is>
+          <t>%1$d초</t>
         </is>
       </c>
     </row>

--- a/tools/language/多语言对照表.xlsx
+++ b/tools/language/多语言对照表.xlsx
@@ -395,7 +395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB566"/>
+  <dimension ref="A1:AB568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31.6299991607666" customWidth="1" min="1" max="1"/>
@@ -29493,6 +29493,70 @@
       <c r="F566" s="5" t="inlineStr">
         <is>
           <t>%1$d초</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>backup_export_limit_exceeded</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>备份内容超出当前支持范围，未导出。现有记录仍保存在此设备上。</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>This backup exceeds the supported size or record limit and was not exported. Your records are still saved on this device.</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>備份內容超出目前支援範圍，未匯出。現有記錄仍儲存在此裝置上。</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>バックアップのサイズまたは記録数が上限を超えたため、書き出せませんでした。記録はこの端末に保存されています。</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>백업 크기 또는 기록 수가 지원 한도를 초과하여 내보내지 못했습니다. 기록은 이 기기에 보관되어 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>backup_export_invalid_data</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>部分记录无法生成可恢复的备份，未导出。现有记录仍保存在此设备上。</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Some records cannot be included in a restorable backup, so nothing was exported. Your records are still saved on this device.</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>部分記錄無法產生可還原的備份，未匯出。現有記錄仍儲存在此裝置上。</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>一部の記録から復元可能なバックアップを作成できないため、書き出せませんでした。記録はこの端末に保存されています。</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>일부 기록을 복원 가능한 백업에 포함할 수 없어 내보내지 못했습니다. 기록은 이 기기에 보관되어 있습니다.</t>
         </is>
       </c>
     </row>

--- a/tools/language/多语言对照表.xlsx
+++ b/tools/language/多语言对照表.xlsx
@@ -395,7 +395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB568"/>
+  <dimension ref="A1:AB569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31.6299991607666" customWidth="1" min="1" max="1"/>
@@ -29557,6 +29557,38 @@
       <c r="F568" t="inlineStr">
         <is>
           <t>일부 기록을 복원 가능한 백업에 포함할 수 없어 내보내지 못했습니다. 기록은 이 기기에 보관되어 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>backup_import_ambiguous_baby</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>部分宝宝的对应关系不明确，未合并。现有记录未改变。</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Some babies could not be matched safely. The backup was not merged, and your records are unchanged.</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>部分寶寶的對應關係不明確，未合併。現有記錄未變更。</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>一部のお子さまの対応関係を特定できないため、バックアップを統合しませんでした。既存の記録は変更されていません。</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>일부 아기의 일치 여부를 명확히 확인할 수 없어 백업을 병합하지 않았습니다. 기존 기록은 변경되지 않았습니다.</t>
         </is>
       </c>
     </row>

--- a/tools/language/多语言对照表.xlsx
+++ b/tools/language/多语言对照表.xlsx
@@ -5011,7 +5011,7 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Total %1$d minutes</t>
+          <t>Total %1$d min</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -16729,7 +16729,7 @@
       </c>
       <c r="C301" s="5" t="inlineStr">
         <is>
-          <t>%1$d hours %2$d minutes</t>
+          <t>%1$d hr %2$d min</t>
         </is>
       </c>
       <c r="D301" s="5" t="inlineStr">
@@ -16783,7 +16783,7 @@
       </c>
       <c r="C302" s="5" t="inlineStr">
         <is>
-          <t>%1$d minutes</t>
+          <t>%1$d min</t>
         </is>
       </c>
       <c r="D302" s="5" t="inlineStr">
@@ -24775,7 +24775,7 @@
       </c>
       <c r="C450" s="5" t="inlineStr">
         <is>
-          <t>%1$d times / %2$s</t>
+          <t>Count: %1$d · %2$s</t>
         </is>
       </c>
       <c r="D450" s="5" t="inlineStr">
@@ -24829,7 +24829,7 @@
       </c>
       <c r="C451" s="5" t="inlineStr">
         <is>
-          <t>%1$d times / %2$s</t>
+          <t>Count: %1$d · %2$s</t>
         </is>
       </c>
       <c r="D451" s="5" t="inlineStr">
@@ -24883,7 +24883,7 @@
       </c>
       <c r="C452" s="5" t="inlineStr">
         <is>
-          <t>%1$d times</t>
+          <t>Count: %1$d</t>
         </is>
       </c>
       <c r="D452" s="5" t="inlineStr">
@@ -25261,7 +25261,7 @@
       </c>
       <c r="C459" s="5" t="inlineStr">
         <is>
-          <t>%1$d times / %2$d%%</t>
+          <t>Count: %1$d · %2$d%%</t>
         </is>
       </c>
       <c r="D459" s="5" t="inlineStr">
@@ -25747,7 +25747,7 @@
       </c>
       <c r="C468" s="5" t="inlineStr">
         <is>
-          <t>Health events %1$d times</t>
+          <t>Health records: %1$d</t>
         </is>
       </c>
       <c r="D468" s="5" t="inlineStr">
@@ -25801,7 +25801,7 @@
       </c>
       <c r="C469" s="5" t="inlineStr">
         <is>
-          <t>Temperature %1$d times</t>
+          <t>Temperature checks: %1$d</t>
         </is>
       </c>
       <c r="D469" s="5" t="inlineStr">
@@ -25855,7 +25855,7 @@
       </c>
       <c r="C470" s="5" t="inlineStr">
         <is>
-          <t>Medicine %1$d times</t>
+          <t>Medication entries: %1$d</t>
         </is>
       </c>
       <c r="D470" s="5" t="inlineStr">
@@ -25909,7 +25909,7 @@
       </c>
       <c r="C471" s="5" t="inlineStr">
         <is>
-          <t>Doctor %1$d times</t>
+          <t>Doctor visits: %1$d</t>
         </is>
       </c>
       <c r="D471" s="5" t="inlineStr">
@@ -25963,7 +25963,7 @@
       </c>
       <c r="C472" s="5" t="inlineStr">
         <is>
-          <t>Symptoms %1$d times</t>
+          <t>Symptom entries: %1$d</t>
         </is>
       </c>
       <c r="D472" s="5" t="inlineStr">
@@ -26017,7 +26017,7 @@
       </c>
       <c r="C473" s="5" t="inlineStr">
         <is>
-          <t>Vaccines %1$d times</t>
+          <t>Vaccinations: %1$d</t>
         </is>
       </c>
       <c r="D473" s="5" t="inlineStr">
@@ -26179,7 +26179,7 @@
       </c>
       <c r="C476" s="5" t="inlineStr">
         <is>
-          <t>%1$d records that day</t>
+          <t>Records: %1$d</t>
         </is>
       </c>
       <c r="D476" s="5" t="inlineStr">
@@ -26719,7 +26719,7 @@
       </c>
       <c r="C486" s="5" t="inlineStr">
         <is>
-          <t>%d times</t>
+          <t>Count: %d</t>
         </is>
       </c>
       <c r="D486" s="5" t="inlineStr">
@@ -26935,7 +26935,7 @@
       </c>
       <c r="C490" s="5" t="inlineStr">
         <is>
-          <t>%d minutes</t>
+          <t>%d min</t>
         </is>
       </c>
       <c r="D490" s="5" t="inlineStr">
@@ -27941,7 +27941,7 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>%1$d minutes ago</t>
+          <t>%1$d min ago</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
@@ -27973,7 +27973,7 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>in %1$d minutes</t>
+          <t>in %1$d min</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
@@ -28005,7 +28005,7 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>%1$d hours ago</t>
+          <t>%1$d hr ago</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
@@ -28037,7 +28037,7 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>in %1$d hours</t>
+          <t>in %1$d hr</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">

--- a/tools/language/多语言对照表.xlsx
+++ b/tools/language/多语言对照表.xlsx
@@ -848,27 +848,27 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · </t>
+          <t>\u0020·\u0020</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · </t>
+          <t>\u0020·\u0020</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · </t>
+          <t>\u0020·\u0020</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · </t>
+          <t>\u0020·\u0020</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · </t>
+          <t>\u0020·\u0020</t>
         </is>
       </c>
       <c r="G7" s="5" t="n"/>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>%1$s%2$d minutes</t>
+          <t>%1$s %2$d min</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -29789,27 +29789,27 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>babycare</t>
+          <t>BabyCare</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>babycare</t>
+          <t>BabyCare</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>babycare</t>
+          <t>BabyCare</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>babycare</t>
+          <t>BabyCare</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>babycare</t>
+          <t>BabyCare</t>
         </is>
       </c>
       <c r="G2" s="5" t="str"/>

--- a/tools/language/多语言对照表.xlsx
+++ b/tools/language/多语言对照表.xlsx
@@ -395,7 +395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB569"/>
+  <dimension ref="A1:AB572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31.6299991607666" customWidth="1" min="1" max="1"/>
@@ -29589,6 +29589,102 @@
       <c r="F569" t="inlineStr">
         <is>
           <t>일부 아기의 일치 여부를 명확히 확인할 수 없어 백업을 병합하지 않았습니다. 기존 기록은 변경되지 않았습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="5" t="inlineStr">
+        <is>
+          <t>prediction_feeding_expired</t>
+        </is>
+      </c>
+      <c r="B570" s="5" t="inlineStr">
+        <is>
+          <t>喂奶预测区间已过</t>
+        </is>
+      </c>
+      <c r="C570" s="5" t="inlineStr">
+        <is>
+          <t>Feeding window has passed</t>
+        </is>
+      </c>
+      <c r="D570" s="5" t="inlineStr">
+        <is>
+          <t>餵奶預測區間已過</t>
+        </is>
+      </c>
+      <c r="E570" s="5" t="inlineStr">
+        <is>
+          <t>授乳の予測時間帯を過ぎました</t>
+        </is>
+      </c>
+      <c r="F570" s="5" t="inlineStr">
+        <is>
+          <t>수유 예상 시간대가 지났어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="5" t="inlineStr">
+        <is>
+          <t>prediction_sleep_expired</t>
+        </is>
+      </c>
+      <c r="B571" s="5" t="inlineStr">
+        <is>
+          <t>睡眠预测区间已过</t>
+        </is>
+      </c>
+      <c r="C571" s="5" t="inlineStr">
+        <is>
+          <t>Sleep window has passed</t>
+        </is>
+      </c>
+      <c r="D571" s="5" t="inlineStr">
+        <is>
+          <t>睡眠預測區間已過</t>
+        </is>
+      </c>
+      <c r="E571" s="5" t="inlineStr">
+        <is>
+          <t>睡眠の予測時間帯を過ぎました</t>
+        </is>
+      </c>
+      <c r="F571" s="5" t="inlineStr">
+        <is>
+          <t>수면 예상 시간대가 지났어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="5" t="inlineStr">
+        <is>
+          <t>prediction_expired_hint</t>
+        </is>
+      </c>
+      <c r="B572" s="5" t="inlineStr">
+        <is>
+          <t>以宝宝实际情况为准，记录后更新预测</t>
+        </is>
+      </c>
+      <c r="C572" s="5" t="inlineStr">
+        <is>
+          <t>Follow your baby’s actual routine; new records update estimates</t>
+        </is>
+      </c>
+      <c r="D572" s="5" t="inlineStr">
+        <is>
+          <t>以寶寶實際情況為準，記錄後更新預測</t>
+        </is>
+      </c>
+      <c r="E572" s="5" t="inlineStr">
+        <is>
+          <t>赤ちゃんの実際の様子を優先し、記録して予測を更新</t>
+        </is>
+      </c>
+      <c r="F572" s="5" t="inlineStr">
+        <is>
+          <t>아기의 실제 상태를 참고해 기록하면 예측이 업데이트돼요</t>
         </is>
       </c>
     </row>

--- a/tools/language/多语言对照表.xlsx
+++ b/tools/language/多语言对照表.xlsx
@@ -395,7 +395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB572"/>
+  <dimension ref="A1:AB576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31.6299991607666" customWidth="1" min="1" max="1"/>
@@ -29685,6 +29685,134 @@
       <c r="F572" s="5" t="inlineStr">
         <is>
           <t>아기의 실제 상태를 참고해 기록하면 예측이 업데이트돼요</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="5" t="inlineStr">
+        <is>
+          <t>legacy_growth_record_title</t>
+        </is>
+      </c>
+      <c r="B573" s="5" t="inlineStr">
+        <is>
+          <t>历史成长记录</t>
+        </is>
+      </c>
+      <c r="C573" s="5" t="inlineStr">
+        <is>
+          <t>Legacy growth record</t>
+        </is>
+      </c>
+      <c r="D573" s="5" t="inlineStr">
+        <is>
+          <t>歷史成長記錄</t>
+        </is>
+      </c>
+      <c r="E573" s="5" t="inlineStr">
+        <is>
+          <t>旧形式の成長記録</t>
+        </is>
+      </c>
+      <c r="F573" s="5" t="inlineStr">
+        <is>
+          <t>이전 형식의 성장 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="5" t="inlineStr">
+        <is>
+          <t>legacy_growth_empty</t>
+        </is>
+      </c>
+      <c r="B574" s="5" t="inlineStr">
+        <is>
+          <t>未填写测量值</t>
+        </is>
+      </c>
+      <c r="C574" s="5" t="inlineStr">
+        <is>
+          <t>No measurements entered</t>
+        </is>
+      </c>
+      <c r="D574" s="5" t="inlineStr">
+        <is>
+          <t>未填寫測量值</t>
+        </is>
+      </c>
+      <c r="E574" s="5" t="inlineStr">
+        <is>
+          <t>測定値が入力されていません</t>
+        </is>
+      </c>
+      <c r="F574" s="5" t="inlineStr">
+        <is>
+          <t>입력된 측정값이 없어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="5" t="inlineStr">
+        <is>
+          <t>legacy_growth_photo_reference</t>
+        </is>
+      </c>
+      <c r="B575" s="5" t="inlineStr">
+        <is>
+          <t>图片引用</t>
+        </is>
+      </c>
+      <c r="C575" s="5" t="inlineStr">
+        <is>
+          <t>Photo reference</t>
+        </is>
+      </c>
+      <c r="D575" s="5" t="inlineStr">
+        <is>
+          <t>圖片參照</t>
+        </is>
+      </c>
+      <c r="E575" s="5" t="inlineStr">
+        <is>
+          <t>画像の参照先</t>
+        </is>
+      </c>
+      <c r="F575" s="5" t="inlineStr">
+        <is>
+          <t>사진 참조</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="5" t="inlineStr">
+        <is>
+          <t>legacy_growth_statistics_hint</t>
+        </is>
+      </c>
+      <c r="B576" s="5" t="inlineStr">
+        <is>
+          <t>旧版记录保留原始测量值，暂不计入成长趋势与百分位。</t>
+        </is>
+      </c>
+      <c r="C576" s="5" t="inlineStr">
+        <is>
+          <t>Legacy records keep their original measurements and are not yet included in growth trends or percentiles.</t>
+        </is>
+      </c>
+      <c r="D576" s="5" t="inlineStr">
+        <is>
+          <t>舊版記錄保留原始測量值，暫不計入成長趨勢與百分位。</t>
+        </is>
+      </c>
+      <c r="E576" s="5" t="inlineStr">
+        <is>
+          <t>旧形式の記録は元の測定値を保持しています。成長傾向とパーセンタイルにはまだ含まれていません。</t>
+        </is>
+      </c>
+      <c r="F576" s="5" t="inlineStr">
+        <is>
+          <t>이전 형식의 기록은 원래 측정값을 유지하며, 아직 성장 추이와 백분위에 포함되지 않아요.</t>
         </is>
       </c>
     </row>

--- a/tools/language/多语言对照表.xlsx
+++ b/tools/language/多语言对照表.xlsx
@@ -29691,128 +29691,128 @@
     <row r="573">
       <c r="A573" s="5" t="inlineStr">
         <is>
-          <t>legacy_growth_record_title</t>
+          <t>statistics_growth_percentile_chart_note</t>
         </is>
       </c>
       <c r="B573" s="5" t="inlineStr">
         <is>
-          <t>历史成长记录</t>
+          <t>各点按测量次序等距排列，间距不代表时间。参考线：P10、P50、P90。</t>
         </is>
       </c>
       <c r="C573" s="5" t="inlineStr">
         <is>
-          <t>Legacy growth record</t>
+          <t>Points are equally spaced in measurement order, not by time. Reference lines: P10, P50, P90.</t>
         </is>
       </c>
       <c r="D573" s="5" t="inlineStr">
         <is>
-          <t>歷史成長記錄</t>
+          <t>各點按測量次序等距排列，間距不代表時間。參考線：P10、P50、P90。</t>
         </is>
       </c>
       <c r="E573" s="5" t="inlineStr">
         <is>
-          <t>旧形式の成長記録</t>
+          <t>各点は測定順に等間隔で並び、間隔は時間を表しません。基準線：P10、P50、P90。</t>
         </is>
       </c>
       <c r="F573" s="5" t="inlineStr">
         <is>
-          <t>이전 형식의 성장 기록</t>
+          <t>점은 측정 순서대로 같은 간격으로 표시되며, 간격은 시간을 나타내지 않아요. 기준선: P10, P50, P90.</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" s="5" t="inlineStr">
         <is>
-          <t>legacy_growth_empty</t>
+          <t>statistics_growth_percentile_period_format</t>
         </is>
       </c>
       <c r="B574" s="5" t="inlineStr">
         <is>
-          <t>未填写测量值</t>
+          <t>最近 %1$d 次有效测量\n%2$s—%3$s</t>
         </is>
       </c>
       <c r="C574" s="5" t="inlineStr">
         <is>
-          <t>No measurements entered</t>
+          <t>Recent valid measurements: %1$d\n%2$s–%3$s</t>
         </is>
       </c>
       <c r="D574" s="5" t="inlineStr">
         <is>
-          <t>未填寫測量值</t>
+          <t>最近 %1$d 次有效測量\n%2$s—%3$s</t>
         </is>
       </c>
       <c r="E574" s="5" t="inlineStr">
         <is>
-          <t>測定値が入力されていません</t>
+          <t>直近の有効な測定：%1$d 回\n%2$s～%3$s</t>
         </is>
       </c>
       <c r="F574" s="5" t="inlineStr">
         <is>
-          <t>입력된 측정값이 없어요</t>
+          <t>최근 유효 측정: %1$d회\n%2$s–%3$s</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" s="5" t="inlineStr">
         <is>
-          <t>legacy_growth_photo_reference</t>
+          <t>statistics_growth_percentile_point_accessibility_format</t>
         </is>
       </c>
       <c r="B575" s="5" t="inlineStr">
         <is>
-          <t>图片引用</t>
+          <t>%1$s，P%2$d</t>
         </is>
       </c>
       <c r="C575" s="5" t="inlineStr">
         <is>
-          <t>Photo reference</t>
+          <t>%1$s, P%2$d</t>
         </is>
       </c>
       <c r="D575" s="5" t="inlineStr">
         <is>
-          <t>圖片參照</t>
+          <t>%1$s，P%2$d</t>
         </is>
       </c>
       <c r="E575" s="5" t="inlineStr">
         <is>
-          <t>画像の参照先</t>
+          <t>%1$s、P%2$d</t>
         </is>
       </c>
       <c r="F575" s="5" t="inlineStr">
         <is>
-          <t>사진 참조</t>
+          <t>%1$s, P%2$d</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" s="5" t="inlineStr">
         <is>
-          <t>legacy_growth_statistics_hint</t>
+          <t>statistics_growth_percentile_chart_accessibility_format</t>
         </is>
       </c>
       <c r="B576" s="5" t="inlineStr">
         <is>
-          <t>旧版记录保留原始测量值，暂不计入成长趋势与百分位。</t>
+          <t>%1$s。%2$s。%3$s</t>
         </is>
       </c>
       <c r="C576" s="5" t="inlineStr">
         <is>
-          <t>Legacy records keep their original measurements and are not yet included in growth trends or percentiles.</t>
+          <t>%1$s. %2$s. %3$s</t>
         </is>
       </c>
       <c r="D576" s="5" t="inlineStr">
         <is>
-          <t>舊版記錄保留原始測量值，暫不計入成長趨勢與百分位。</t>
+          <t>%1$s。%2$s。%3$s</t>
         </is>
       </c>
       <c r="E576" s="5" t="inlineStr">
         <is>
-          <t>旧形式の記録は元の測定値を保持しています。成長傾向とパーセンタイルにはまだ含まれていません。</t>
+          <t>%1$s。%2$s。%3$s</t>
         </is>
       </c>
       <c r="F576" s="5" t="inlineStr">
         <is>
-          <t>이전 형식의 기록은 원래 측정값을 유지하며, 아직 성장 추이와 백분위에 포함되지 않아요.</t>
+          <t>%1$s. %2$s. %3$s</t>
         </is>
       </c>
     </row>

--- a/tools/language/多语言对照表.xlsx
+++ b/tools/language/多语言对照表.xlsx
@@ -395,7 +395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB576"/>
+  <dimension ref="A1:AB590"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31.6299991607666" customWidth="1" min="1" max="1"/>
@@ -29813,6 +29813,454 @@
       <c r="F576" s="5" t="inlineStr">
         <is>
           <t>%1$s. %2$s. %3$s</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>timer_stopped_hint</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>计时已结束，等待保存</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Timing ended · ready to save</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>計時已結束，等待儲存</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>計測終了・保存待ち</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>타이머 종료 · 저장 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>timer_sleep_awake</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>夜间醒了</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Night waking</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>夜間醒了</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>夜中に起きた</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>밤중에 깼어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>timer_sleep_again</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>再次入睡</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Back to sleep</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>再次入睡</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>また眠った</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>다시 잠들었어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>timer_sleep_finish</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>醒了并保存</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Wake up and save</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>醒了並儲存</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>起床して保存</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>일어났어요 · 저장</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>timer_review_title</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>核对计时时间</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Review timer times</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>核對計時時間</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>計測時刻を確認</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>타이머 시간 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>timer_review_required</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>设备重启或时间发生变化，请核对开始、结束时间。确认后将按所示时间修正受影响的片段；暂停间隔仍不计入。</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>The device restarted or its clock changed. Check the start and end times. Confirm to correct affected segments using these times; pauses stay excluded.</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>裝置重新啟動或時間發生變化，請核對開始、結束時間。確認後將按所示時間修正受影響的片段；暫停間隔仍不計入。</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>端末の再起動または時刻変更がありました。開始・終了時刻を確認してください。確認後、該当区間を表示時刻で修正します。一時停止の時間は含みません。</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>기기가 재시작되었거나 시간이 변경되었습니다. 시작과 종료 시간을 확인하세요. 확인하면 해당 구간을 표시된 시간으로 수정하며 일시 정지 시간은 제외됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>timer_invalid_change</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>无法这样修改，请保留已有片段的先后顺序并核对时间</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Check the times and keep the existing segments in order.</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>無法這樣修改，請保留已有片段的先後順序並核對時間</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>既存の区間の順序を保ち、時刻を確認してください</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>기존 구간의 순서를 유지하고 시간을 확인하세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>timer_leave_tip</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>计时会自动保留，可以稍后回来继续；尚未保存的其他输入可能丢失。</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>The timer is saved automatically. You can return later; other unsaved details may be lost.</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>計時會自動保留，可以稍後回來繼續；尚未儲存的其他輸入可能遺失。</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>計測は自動保存され、後で再開できます。他の未保存の入力は失われる場合があります。</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>타이머는 자동 저장되어 나중에 돌아올 수 있습니다. 저장하지 않은 다른 입력은 사라질 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>timer_discard</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>放弃计时</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Discard timer</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>放棄計時</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>計測を破棄</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>타이머 버리기</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>timer_discard_confirm</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>放弃后将删除这次未完成记录及计时片段，是否继续？</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Delete this unfinished record and its timed segments?</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>放棄後將刪除這次未完成記錄及計時片段，是否繼續？</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>この未完了の記録と計測区間を削除しますか？</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>완료되지 않은 기록과 시간 구간을 삭제할까요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>timer_sleep_paused</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>睡眠已暂停</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Sleep paused</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>睡眠已暫停</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>睡眠を一時停止中</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>수면 일시 정지</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>timer_feeding_paused</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>喂养已暂停</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Feeding paused</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>餵養已暫停</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>授乳を一時停止中</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>수유 일시 정지</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>timer_open_record</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>继续处理记录</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Open record</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>繼續處理記錄</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>記録を開く</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>기록 열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>timer_part_unspecified</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>未区分侧别</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Unspecified side</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>未區分側別</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>左右未指定</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>방향 미지정</t>
         </is>
       </c>
     </row>
